--- a/데이터 베이스/final_data.xlsx
+++ b/데이터 베이스/final_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jun_lab\Desktop\code\Punching-shear\데이터 베이스\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SSC-3\Desktop\code\Punching-shear\데이터 베이스\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C1DA3F0-02F3-44D5-85DF-B381DCB5E320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE9B3E6C-AD20-4F29-9CCA-89A52DD3CA84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3360" yWindow="2310" windowWidth="28800" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5355" yWindow="1125" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NEES_Database__ACI_445_Punching" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -731,9 +734,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -771,7 +774,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -877,7 +880,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1019,7 +1022,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2506,6 +2509,9 @@
       <c r="A47">
         <v>50</v>
       </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
       <c r="C47">
         <v>3.669724770642202</v>
       </c>
@@ -7079,6 +7085,9 @@
       <c r="A190">
         <v>210</v>
       </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
       <c r="C190">
         <v>1.7482517482517483</v>
       </c>
@@ -7108,6 +7117,9 @@
       <c r="A191">
         <v>211</v>
       </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
       <c r="C191">
         <v>2.3148148148148149</v>
       </c>
@@ -7137,6 +7149,9 @@
       <c r="A192">
         <v>212</v>
       </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
       <c r="C192">
         <v>2.2727272727272729</v>
       </c>
@@ -7166,6 +7181,9 @@
       <c r="A193">
         <v>213</v>
       </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
       <c r="C193">
         <v>2.2727272727272729</v>
       </c>
@@ -7195,6 +7213,9 @@
       <c r="A194">
         <v>214</v>
       </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
       <c r="C194">
         <v>2.2727272727272729</v>
       </c>
@@ -7224,6 +7245,9 @@
       <c r="A195">
         <v>215</v>
       </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
       <c r="C195">
         <v>2.2727272727272729</v>
       </c>
@@ -7253,6 +7277,9 @@
       <c r="A196">
         <v>216</v>
       </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
       <c r="C196">
         <v>2.2727272727272729</v>
       </c>
@@ -7282,6 +7309,9 @@
       <c r="A197">
         <v>217</v>
       </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
       <c r="C197">
         <v>2.2727272727272729</v>
       </c>
@@ -7311,6 +7341,9 @@
       <c r="A198">
         <v>218</v>
       </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
       <c r="C198">
         <v>2.3148148148148149</v>
       </c>
@@ -7340,6 +7373,9 @@
       <c r="A199">
         <v>219</v>
       </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
       <c r="C199">
         <v>2.2321428571428572</v>
       </c>
@@ -7369,6 +7405,9 @@
       <c r="A200">
         <v>220</v>
       </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
       <c r="C200">
         <v>2.2727272727272729</v>
       </c>
@@ -7398,6 +7437,9 @@
       <c r="A201">
         <v>221</v>
       </c>
+      <c r="B201">
+        <v>0</v>
+      </c>
       <c r="C201">
         <v>1.5909090909090908</v>
       </c>
@@ -7427,6 +7469,9 @@
       <c r="A202">
         <v>222</v>
       </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
       <c r="C202">
         <v>1.5909090909090908</v>
       </c>
@@ -10368,6 +10413,9 @@
       <c r="A294">
         <v>321</v>
       </c>
+      <c r="B294">
+        <v>0</v>
+      </c>
       <c r="C294">
         <v>2.393700787401575</v>
       </c>
@@ -10589,6 +10637,9 @@
       <c r="A301">
         <v>328</v>
       </c>
+      <c r="B301">
+        <v>0</v>
+      </c>
       <c r="C301">
         <v>1.9947506561679789</v>
       </c>
@@ -10618,6 +10669,9 @@
       <c r="A302">
         <v>329</v>
       </c>
+      <c r="B302">
+        <v>0</v>
+      </c>
       <c r="C302">
         <v>2.9921259842519685</v>
       </c>
@@ -10647,6 +10701,9 @@
       <c r="A303">
         <v>330</v>
       </c>
+      <c r="B303">
+        <v>0</v>
+      </c>
       <c r="C303">
         <v>3.9895013123359577</v>
       </c>
@@ -10676,6 +10733,9 @@
       <c r="A304">
         <v>331</v>
       </c>
+      <c r="B304">
+        <v>0</v>
+      </c>
       <c r="C304">
         <v>2.9921259842519685</v>
       </c>
@@ -10705,6 +10765,9 @@
       <c r="A305">
         <v>332</v>
       </c>
+      <c r="B305">
+        <v>0</v>
+      </c>
       <c r="C305">
         <v>6.0104986876640414</v>
       </c>
@@ -10734,6 +10797,9 @@
       <c r="A306">
         <v>333</v>
       </c>
+      <c r="B306">
+        <v>0</v>
+      </c>
       <c r="C306">
         <v>8.0052493438320216</v>
       </c>
@@ -10763,6 +10829,9 @@
       <c r="A307">
         <v>334</v>
       </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
       <c r="C307">
         <v>1.9947506561679789</v>
       </c>
@@ -10792,6 +10861,9 @@
       <c r="A308">
         <v>335</v>
       </c>
+      <c r="B308">
+        <v>0</v>
+      </c>
       <c r="C308">
         <v>3.9895013123359577</v>
       </c>
@@ -10821,6 +10893,9 @@
       <c r="A309">
         <v>336</v>
       </c>
+      <c r="B309">
+        <v>0</v>
+      </c>
       <c r="C309">
         <v>5.879265091863517</v>
       </c>
@@ -10850,6 +10925,9 @@
       <c r="A310">
         <v>337</v>
       </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
       <c r="C310">
         <v>8.0052493438320216</v>
       </c>
@@ -10879,6 +10957,9 @@
       <c r="A311">
         <v>338</v>
       </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
       <c r="C311">
         <v>1.9947506561679789</v>
       </c>
@@ -10908,6 +10989,9 @@
       <c r="A312">
         <v>339</v>
       </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
       <c r="C312">
         <v>4.0419947506561682</v>
       </c>
@@ -10937,6 +11021,9 @@
       <c r="A313">
         <v>340</v>
       </c>
+      <c r="B313">
+        <v>0</v>
+      </c>
       <c r="C313">
         <v>7.9265091863517059</v>
       </c>
@@ -10966,6 +11053,9 @@
       <c r="A314">
         <v>341</v>
       </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
       <c r="C314">
         <v>6.0104986876640414</v>
       </c>
@@ -10994,6 +11084,9 @@
     <row r="315" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>342</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
       </c>
       <c r="C315">
         <v>4.0419947506561682</v>
